--- a/files/港岛-北角-海璇.xlsx
+++ b/files/港岛-北角-海璇.xlsx
@@ -864,7 +864,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2020-01-21</t>
+          <t>2020-01-22</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -996,7 +996,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2019-05-13</t>
+          <t>2019-05-14</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2018-06-12</t>
+          <t>2018-06-13</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2019-01-10</t>
+          <t>2019-01-11</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2018-06-03</t>
+          <t>2018-06-04</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2018-05-01</t>
+          <t>2018-05-02</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2018-01-24</t>
+          <t>2018-01-25</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2018-01-24</t>
+          <t>2018-01-25</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2018-01-09</t>
+          <t>2018-01-10</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2018-01-09</t>
+          <t>2018-01-10</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2019-08-20</t>
+          <t>2019-08-21</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2019-01-03</t>
+          <t>2019-01-04</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2018-04-16</t>
+          <t>2018-04-17</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2018-05-16</t>
+          <t>2018-05-17</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2018-05-10</t>
+          <t>2018-05-11</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2018-06-05</t>
+          <t>2018-06-06</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2018-04-25</t>
+          <t>2018-04-26</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2018-04-22</t>
+          <t>2018-04-23</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2019-03-20</t>
+          <t>2019-03-21</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2021-03-30</t>
+          <t>2021-03-31</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2021-11-18</t>
+          <t>2021-11-19</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2018-10-28</t>
+          <t>2018-10-29</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2018-08-05</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2018-04-17</t>
+          <t>2018-04-18</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2018-06-20</t>
+          <t>2018-06-21</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2018-06-20</t>
+          <t>2018-06-21</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2018-01-29</t>
+          <t>2018-01-30</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2018-01-28</t>
+          <t>2018-01-29</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2021-12-08</t>
+          <t>2021-12-09</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2018-01-31</t>
+          <t>2018-02-01</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2019-01-08</t>
+          <t>2019-01-09</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2018-05-23</t>
+          <t>2018-05-24</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2018-04-16</t>
+          <t>2018-04-17</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2018-06-19</t>
+          <t>2018-06-20</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2019-01-29</t>
+          <t>2019-01-30</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2018-07-04</t>
+          <t>2018-07-05</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2021-05-04</t>
+          <t>2021-05-05</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2024-10-07</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2018-06-10</t>
+          <t>2018-06-11</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2023-03-09</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2018-08-05</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2018-08-07</t>
+          <t>2018-08-08</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2018-08-07</t>
+          <t>2018-08-08</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2019-01-07</t>
+          <t>2019-01-08</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2018-10-24</t>
+          <t>2018-10-25</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2018-08-02</t>
+          <t>2018-08-03</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2018-08-14</t>
+          <t>2018-08-15</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2018-08-16</t>
+          <t>2018-08-17</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2019-05-22</t>
+          <t>2019-05-23</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7370,7 +7370,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2019-04-14</t>
+          <t>2019-04-15</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2019-07-04</t>
+          <t>2019-07-05</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2019-05-21</t>
+          <t>2019-05-22</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2019-07-10</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7618,7 +7618,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2019-10-15</t>
+          <t>2019-10-16</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
+          <t>2020-07-15</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2018-07-31</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2018-07-31</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2019-04-11</t>
+          <t>2019-04-12</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2019-04-22</t>
+          <t>2019-04-23</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2018-08-07</t>
+          <t>2018-08-08</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2018-08-07</t>
+          <t>2018-08-08</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2018-08-07</t>
+          <t>2018-08-08</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2020-06-24</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8734,7 +8734,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2018-07-29</t>
+          <t>2018-07-30</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2018-07-29</t>
+          <t>2018-07-30</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2019-02-14</t>
+          <t>2019-02-15</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2019-01-06</t>
+          <t>2019-01-07</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2019-04-10</t>
+          <t>2019-04-11</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2020-07-02</t>
+          <t>2020-07-03</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2021-11-17</t>
+          <t>2021-11-18</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9540,7 +9540,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2019-08-27</t>
+          <t>2019-08-28</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>2018-08-14</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2018-08-08</t>
+          <t>2018-08-09</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2018-09-02</t>
+          <t>2018-09-03</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2018-07-30</t>
+          <t>2018-07-31</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9912,7 +9912,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2018-08-07</t>
+          <t>2018-08-08</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -10036,7 +10036,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2018-08-07</t>
+          <t>2018-08-08</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -10160,7 +10160,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2018-08-07</t>
+          <t>2018-08-08</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2018-07-29</t>
+          <t>2018-07-30</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10346,7 +10346,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2018-08-12</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10408,7 +10408,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2018-08-07</t>
+          <t>2018-08-08</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10470,7 +10470,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2018-07-29</t>
+          <t>2018-07-30</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10532,7 +10532,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2018-07-29</t>
+          <t>2018-07-30</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10594,7 +10594,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2018-07-29</t>
+          <t>2018-07-30</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10718,7 +10718,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2018-07-31</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10780,7 +10780,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2018-08-05</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2018-08-05</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2018-08-06</t>
+          <t>2018-08-07</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10966,7 +10966,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2018-08-05</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2020-12-13</t>
+          <t>2020-12-14</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2018-08-02</t>
+          <t>2018-08-03</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -11152,7 +11152,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2018-08-14</t>
+          <t>2018-08-15</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2018-07-31</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2018-08-12</t>
+          <t>2018-08-13</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11338,7 +11338,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2018-08-29</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2019-05-16</t>
+          <t>2019-05-17</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2018-08-27</t>
+          <t>2018-08-28</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2018-08-09</t>
+          <t>2018-08-10</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2018-08-29</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2018-08-29</t>
+          <t>2018-08-30</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11710,7 +11710,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>2018-08-29</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2018-08-02</t>
+          <t>2018-08-03</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2018-07-29</t>
+          <t>2018-07-30</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2018-08-05</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2018-08-05</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -12020,7 +12020,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2018-07-30</t>
+          <t>2018-07-31</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2018-07-30</t>
+          <t>2018-07-31</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2018-07-29</t>
+          <t>2018-07-30</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2018-08-15</t>
+          <t>2018-08-16</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2018-08-05</t>
+          <t>2018-08-06</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2019-05-01</t>
+          <t>2019-05-02</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2018-07-31</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12454,7 +12454,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2018-07-31</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -13216,7 +13216,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -13278,7 +13278,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2025-07-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2023-12-13</t>
+          <t>2023-12-14</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13922,7 +13922,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -14302,7 +14302,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -24439,7 +24439,7 @@
           <t>A | 2031呎 (4+房)
 $15304万
 $75,350/呎
-(20年-01月-21日)</t>
+(20年-01月-22日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -24455,7 +24455,7 @@
           <t>A | 1585呎 (4+房)
 $10355万
 $65,330/呎
-(19年-05月-13日)</t>
+(19年-05月-14日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -24478,7 +24478,7 @@
           <t>A | 1585呎 (4+房)
 $9780万
 $61,703/呎
-(19年-01月-10日)</t>
+(19年-01月-11日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -24486,7 +24486,7 @@
           <t>B | 1173呎 (3房)
 $6745万
 $57,500/呎
-(18年-06月-12日)</t>
+(18年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -24501,7 +24501,7 @@
           <t>A | 1585呎 (4+房)
 $8927万
 $56,324/呎
-(18年-05月-01日)</t>
+(18年-05月-02日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -24509,7 +24509,7 @@
           <t>B | 1173呎 (3房)
 $6629万
 $56,513/呎
-(18年-06月-03日)</t>
+(18年-06月-04日)</t>
         </is>
       </c>
     </row>
@@ -24524,7 +24524,7 @@
           <t>A | 1585呎 (4+房)
 $10285万
 $64,887/呎
-(18年-01月-24日)</t>
+(18年-01月-25日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -24532,7 +24532,7 @@
           <t>B | 1173呎 (3房)
 $7217万
 $61,527/呎
-(18年-01月-24日)</t>
+(18年-01月-25日)</t>
         </is>
       </c>
     </row>
@@ -24547,7 +24547,7 @@
           <t>A | 1585呎 (4+房)
 $8981万
 $56,660/呎
-(18年-01月-09日)</t>
+(18年-01月-10日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -24555,7 +24555,7 @@
           <t>B | 1173呎 (3房)
 $6873万
 $58,597/呎
-(18年-01月-09日)</t>
+(18年-01月-10日)</t>
         </is>
       </c>
     </row>
@@ -24570,7 +24570,7 @@
           <t>A | 1585呎 (4+房)
 $8876万
 $56,000/呎
-(19年-01月-03日)</t>
+(19年-01月-04日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -24578,7 +24578,7 @@
           <t>B | 1129呎 (3房)
 $6228万
 $55,164/呎
-(19年-08月-20日)</t>
+(19年-08月-21日)</t>
         </is>
       </c>
     </row>
@@ -24593,7 +24593,7 @@
           <t>A | 1540呎 (4+房)
 $9935万
 $64,513/呎
-(18年-05月-16日)</t>
+(18年-05月-17日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -24601,7 +24601,7 @@
           <t>B | 1173呎 (3房)
 $6389万
 $54,465/呎
-(18年-04月-16日)</t>
+(18年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -24616,7 +24616,7 @@
           <t>A | 1540呎 (4+房)
 $8198万
 $53,235/呎
-(18年-06月-05日)</t>
+(18年-06月-06日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -24624,7 +24624,7 @@
           <t>B | 1173呎 (3房)
 $6690万
 $57,033/呎
-(18年-05月-10日)</t>
+(18年-05月-11日)</t>
         </is>
       </c>
     </row>
@@ -24647,7 +24647,7 @@
           <t>B | 1173呎 (3房)
 $6104万
 $52,036/呎
-(18年-04月-25日)</t>
+(18年-04月-26日)</t>
         </is>
       </c>
     </row>
@@ -24662,7 +24662,7 @@
           <t>A | 1585呎 (4+房)
 $8000万
 $50,473/呎
-(19年-03月-20日)</t>
+(19年-03月-21日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -24670,7 +24670,7 @@
           <t>B | 1173呎 (3房)
 $5706万
 $48,642/呎
-(18年-04月-22日)</t>
+(18年-04月-23日)</t>
         </is>
       </c>
     </row>
@@ -24685,7 +24685,7 @@
           <t>A | 1524呎 (4+房)
 $8389万
 $55,045/呎
-(21年-03月-30日)</t>
+(21年-03月-31日)</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -24835,7 +24835,7 @@
           <t>A | 2322呎 (4+房)
 $20000万
 $86,133/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr"/>
@@ -24851,7 +24851,7 @@
           <t>A | 1555呎 (4+房)
 $10900万
 $70,096/呎
-(21年-11月-18日)</t>
+(21年-11月-19日)</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
@@ -24874,7 +24874,7 @@
           <t>A | 1599呎 (4+房)
 $10237万
 $64,024/呎
-(18年-10月-28日)</t>
+(18年-10月-29日)</t>
         </is>
       </c>
       <c r="C8" s="24" t="inlineStr">
@@ -24897,7 +24897,7 @@
           <t>A | 1555呎 (4+房)
 $10006万
 $64,344/呎
-(18年-08月-05日)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -24920,7 +24920,7 @@
           <t>A | 1599呎 (4+房)
 $10529万
 $65,846/呎
-(18年-04月-17日)</t>
+(18年-04月-18日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -24943,7 +24943,7 @@
           <t>A | 1599呎 (4+房)
 $9198万
 $57,523/呎
-(18年-06月-20日)</t>
+(18年-06月-21日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -24951,7 +24951,7 @@
           <t>B | 1423呎 (4+房)
 $7852万
 $55,181/呎
-(18年-06月-20日)</t>
+(18年-06月-21日)</t>
         </is>
       </c>
     </row>
@@ -24966,7 +24966,7 @@
           <t>A | 1599呎 (4+房)
 $9513万
 $59,493/呎
-(18年-01月-28日)</t>
+(18年-01月-29日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -24974,7 +24974,7 @@
           <t>B | 1467呎 (4+房)
 $8274万
 $56,403/呎
-(18年-01月-29日)</t>
+(18年-01月-30日)</t>
         </is>
       </c>
     </row>
@@ -24989,7 +24989,7 @@
           <t>A | 1599呎 (4+房)
 $950万
 $5,940/呎
-(18年-01月-31日)</t>
+(18年-02月-01日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -24997,7 +24997,7 @@
           <t>B | 1423呎 (4+房)
 $7628万
 $53,608/呎
-(21年-12月-08日)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
     </row>
@@ -25012,7 +25012,7 @@
           <t>A | 1599呎 (4+房)
 $9596万
 $60,010/呎
-(18年-05月-23日)</t>
+(18年-05月-24日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -25020,7 +25020,7 @@
           <t>B | 1423呎 (4+房)
 $1429万
 $10,042/呎
-(19年-01月-08日)</t>
+(19年-01月-09日)</t>
         </is>
       </c>
     </row>
@@ -25043,7 +25043,7 @@
           <t>B | 1467呎 (4+房)
 $8000万
 $54,533/呎
-(18年-04月-16日)</t>
+(18年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -25058,7 +25058,7 @@
           <t>A | 1599呎 (4+房)
 $8319万
 $52,024/呎
-(18年-06月-19日)</t>
+(18年-06月-20日)</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -25089,7 +25089,7 @@
           <t>B | 1467呎 (4+房)
 $6904万
 $47,061/呎
-(19年-01月-29日)</t>
+(19年-01月-30日)</t>
         </is>
       </c>
     </row>
@@ -25104,7 +25104,7 @@
           <t>A | 1599呎 (4+房)
 $7391万
 $46,224/呎
-(18年-07月-04日)</t>
+(18年-07月-05日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -25127,7 +25127,7 @@
           <t>A | 1485呎 (4+房)
 $9848万
 $66,320/呎
-(21年-05月-04日)</t>
+(21年-05月-05日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -25362,7 +25362,7 @@
           <t>A | 1456呎 (4+房)
 $5939万
 $40,789/呎
-(24年-10月-07日)</t>
+(24年-10月-08日)</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -25592,7 +25592,7 @@
           <t>A | 1456呎 (4+房)
 $7391万
 $50,764/呎
-(18年-06月-10日)</t>
+(18年-06月-11日)</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">
@@ -25773,7 +25773,7 @@
           <t>A | 764呎 (2房)
 $4360万
 $57,075/呎
-(23年-03月-09日)</t>
+(23年-03月-10日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -25814,7 +25814,7 @@
           <t>A | 364呎 (1房)
 $1768万
 $48,582/呎
-(18年-10月-24日)</t>
+(18年-10月-25日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -25822,7 +25822,7 @@
           <t>B | 718呎 (2房)
 $3920万
 $54,596/呎
-(19年-01月-07日)</t>
+(19年-01月-08日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -25831,7 +25831,7 @@
           <t>D | 380呎 (1房)
 $1329万
 $34,977/呎
-(18年-08月-07日)</t>
+(18年-08月-08日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -25839,7 +25839,7 @@
           <t>E | 369呎 (1房)
 $1285万
 $34,837/呎
-(18年-08月-07日)</t>
+(18年-08月-08日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -25847,7 +25847,7 @@
           <t>F | 286呎 (开放式)
 $1083万
 $37,863/呎
-(18年-08月-05日)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
     </row>
@@ -25862,7 +25862,7 @@
           <t>A | 364呎 (1房)
 $1544万
 $42,407/呎
-(18年-08月-09日)</t>
+(18年-08月-10日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -25870,7 +25870,7 @@
           <t>B | 378呎 (1房)
 $1848万
 $48,893/呎
-(18年-08月-16日)</t>
+(18年-08月-17日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -25878,7 +25878,7 @@
           <t>C | 524呎 (2房)
 $2333万
 $44,527/呎
-(18年-08月-14日)</t>
+(18年-08月-15日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -25886,7 +25886,7 @@
           <t>D | 380呎 (1房)
 $1321万
 $34,751/呎
-(18年-08月-02日)</t>
+(18年-08月-03日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -25894,7 +25894,7 @@
           <t>E | 369呎 (1房)
 $1277万
 $34,612/呎
-(18年-08月-06日)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -25902,7 +25902,7 @@
           <t>F | 286呎 (开放式)
 $1076万
 $37,620/呎
-(18年-08月-06日)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
           <t>A | 364呎 (1房)
 $1605万
 $44,087/呎
-(19年-10月-15日)</t>
+(19年-10月-16日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -25925,7 +25925,7 @@
           <t>B | 378呎 (1房)
 $1714万
 $45,343/呎
-(19年-07月-10日)</t>
+(19年-07月-11日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -25933,7 +25933,7 @@
           <t>C | 524呎 (2房)
 $2391万
 $45,629/呎
-(19年-05月-21日)</t>
+(19年-05月-22日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -25941,7 +25941,7 @@
           <t>D | 380呎 (1房)
 $1366万
 $35,938/呎
-(19年-07月-04日)</t>
+(19年-07月-05日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -25949,7 +25949,7 @@
           <t>E | 369呎 (1房)
 $1341万
 $36,331/呎
-(19年-04月-14日)</t>
+(19年-04月-15日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -25957,7 +25957,7 @@
           <t>F | 286呎 (开放式)
 $1091万
 $38,146/呎
-(19年-05月-22日)</t>
+(19年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -25972,7 +25972,7 @@
           <t>A | 364呎 (1房)
 $1528万
 $41,988/呎
-(18年-08月-09日)</t>
+(18年-08月-10日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -25980,7 +25980,7 @@
           <t>B | 378呎 (1房)
 $1656万
 $43,811/呎
-(18年-08月-09日)</t>
+(18年-08月-10日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -25988,7 +25988,7 @@
           <t>C | 524呎 (2房)
 $2310万
 $44,086/呎
-(18年-08月-09日)</t>
+(18年-08月-10日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -25996,7 +25996,7 @@
           <t>D | 380呎 (1房)
 $1339万
 $35,235/呎
-(18年-08月-09日)</t>
+(18年-08月-10日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -26012,7 +26012,7 @@
           <t>F | 286呎 (开放式)
 $1091万
 $38,146/呎
-(20年-07月-14日)</t>
+(20年-07月-15日)</t>
         </is>
       </c>
     </row>
@@ -26035,7 +26035,7 @@
           <t>B | 378呎 (1房)
 $1680万
 $44,456/呎
-(19年-04月-22日)</t>
+(19年-04月-23日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -26043,7 +26043,7 @@
           <t>C | 524呎 (2房)
 $2344万
 $44,735/呎
-(19年-04月-11日)</t>
+(19年-04月-12日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -26051,7 +26051,7 @@
           <t>D | 380呎 (1房)
 $1300万
 $34,203/呎
-(18年-07月-31日)</t>
+(18年-08月-01日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -26059,7 +26059,7 @@
           <t>E | 369呎 (1房)
 $1257万
 $34,066/呎
-(18年-07月-31日)</t>
+(18年-08月-01日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -26082,7 +26082,7 @@
           <t>A | 364呎 (1房)
 $1488万
 $40,878/呎
-(18年-08月-09日)</t>
+(18年-08月-10日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -26090,7 +26090,7 @@
           <t>B | 378呎 (1房)
 $1781万
 $47,129/呎
-(18年-08月-09日)</t>
+(18年-08月-10日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -26098,7 +26098,7 @@
           <t>C | 524呎 (2房)
 $1980万
 $37,786/呎
-(20年-06月-23日)</t>
+(20年-06月-24日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -26106,7 +26106,7 @@
           <t>D | 379呎 (1房)
 $1320万
 $34,821/呎
-(18年-08月-07日)</t>
+(18年-08月-08日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -26114,7 +26114,7 @@
           <t>E | 369呎 (1房)
 $1410万
 $38,221/呎
-(18年-08月-07日)</t>
+(18年-08月-08日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -26122,7 +26122,7 @@
           <t>F | 286呎 (开放式)
 $1075万
 $37,600/呎
-(18年-08月-07日)</t>
+(18年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -26137,7 +26137,7 @@
           <t>A | 364呎 (1房)
 $1551万
 $42,623/呎
-(19年-04月-10日)</t>
+(19年-04月-11日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -26145,7 +26145,7 @@
           <t>B | 378呎 (1房)
 $1657万
 $43,840/呎
-(19年-01月-06日)</t>
+(19年-01月-07日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -26153,7 +26153,7 @@
           <t>C | 524呎 (2房)
 $2312万
 $44,115/呎
-(19年-02月-14日)</t>
+(19年-02月-15日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -26161,7 +26161,7 @@
           <t>D | 379呎 (1房)
 $1424万
 $37,571/呎
-(18年-08月-06日)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -26169,7 +26169,7 @@
           <t>E | 369呎 (1房)
 $1477万
 $40,031/呎
-(18年-07月-29日)</t>
+(18年-07月-30日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -26177,7 +26177,7 @@
           <t>F | 286呎 (开放式)
 $1050万
 $36,713/呎
-(18年-07月-29日)</t>
+(18年-07月-30日)</t>
         </is>
       </c>
     </row>
@@ -26208,7 +26208,7 @@
           <t>C | 524呎 (2房)
 $2340万
 $44,655/呎
-(21年-11月-17日)</t>
+(21年-11月-18日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -26224,7 +26224,7 @@
           <t>E | 369呎 (1房)
 $1456万
 $39,453/呎
-(20年-07月-02日)</t>
+(20年-07月-03日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -26247,7 +26247,7 @@
           <t>A | 364呎 (1房)
 $1457万
 $40,030/呎
-(18年-07月-30日)</t>
+(18年-07月-31日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -26263,7 +26263,7 @@
           <t>C | 524呎 (2房)
 $2202万
 $42,032/呎
-(18年-09月-02日)</t>
+(18年-09月-03日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -26271,7 +26271,7 @@
           <t>D | 380呎 (1房)
 $1306万
 $34,367/呎
-(18年-08月-08日)</t>
+(18年-08月-09日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -26279,7 +26279,7 @@
           <t>E | 369呎 (1房)
 $1263万
 $34,231/呎
-(18年-08月-13日)</t>
+(18年-08月-14日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -26287,7 +26287,7 @@
           <t>F | 286呎 (开放式)
 $1176万
 $41,110/呎
-(19年-08月-27日)</t>
+(19年-08月-28日)</t>
         </is>
       </c>
     </row>
@@ -26302,7 +26302,7 @@
           <t>A | 364呎 (1房)
 $1447万
 $39,750/呎
-(18年-08月-06日)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -26310,7 +26310,7 @@
           <t>B | 378呎 (1房)
 $1568万
 $41,479/呎
-(18年-08月-07日)</t>
+(18年-08月-08日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -26318,7 +26318,7 @@
           <t>C | 524呎 (2房)
 $2187万
 $41,738/呎
-(18年-08月-06日)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -26326,7 +26326,7 @@
           <t>D | 380呎 (1房)
 $1277万
 $33,611/呎
-(18年-08月-07日)</t>
+(18年-08月-08日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -26334,7 +26334,7 @@
           <t>E | 369呎 (1房)
 $1235万
 $33,476/呎
-(18年-08月-06日)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -26342,7 +26342,7 @@
           <t>F | 286呎 (开放式)
 $1041万
 $36,385/呎
-(18年-08月-07日)</t>
+(18年-08月-08日)</t>
         </is>
       </c>
     </row>
@@ -26357,7 +26357,7 @@
           <t>A | 364呎 (1房)
 $1437万
 $39,472/呎
-(18年-07月-29日)</t>
+(18年-07月-30日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -26365,7 +26365,7 @@
           <t>B | 378呎 (1房)
 $1557万
 $41,188/呎
-(18年-07月-29日)</t>
+(18年-07月-30日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -26373,7 +26373,7 @@
           <t>C | 524呎 (2房)
 $2172万
 $41,446/呎
-(18年-07月-29日)</t>
+(18年-07月-30日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -26381,7 +26381,7 @@
           <t>D | 380呎 (1房)
 $1376万
 $36,216/呎
-(18年-08月-07日)</t>
+(18年-08月-08日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -26389,7 +26389,7 @@
           <t>E | 369呎 (1房)
 $1232万
 $33,390/呎
-(18年-08月-12日)</t>
+(18年-08月-13日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -26397,7 +26397,7 @@
           <t>F | 286呎 (开放式)
 $1038万
 $36,294/呎
-(18年-07月-29日)</t>
+(18年-07月-30日)</t>
         </is>
       </c>
     </row>
@@ -26412,7 +26412,7 @@
           <t>A | 364呎 (1房)
 $1437万
 $39,472/呎
-(18年-08月-05日)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -26420,7 +26420,7 @@
           <t>B | 378呎 (1房)
 $1557万
 $41,188/呎
-(18年-08月-06日)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -26428,7 +26428,7 @@
           <t>C | 524呎 (2房)
 $2172万
 $41,446/呎
-(18年-08月-05日)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -26436,7 +26436,7 @@
           <t>D | 380呎 (1房)
 $1408万
 $37,043/呎
-(18年-08月-05日)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -26444,7 +26444,7 @@
           <t>E | 369呎 (1房)
 $1232万
 $33,390/呎
-(18年-07月-31日)</t>
+(18年-08月-01日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -26452,7 +26452,7 @@
           <t>F | 286呎 (开放式)
 $1038万
 $36,294/呎
-(18年-08月-06日)</t>
+(18年-08月-07日)</t>
         </is>
       </c>
     </row>
@@ -26467,7 +26467,7 @@
           <t>A | 364呎 (1房)
 $1445万
 $39,699/呎
-(18年-08月-28日)</t>
+(18年-08月-29日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -26475,7 +26475,7 @@
           <t>B | 378呎 (1房)
 $1566万
 $41,424/呎
-(18年-08月-12日)</t>
+(18年-08月-13日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -26483,7 +26483,7 @@
           <t>C | 524呎 (2房)
 $2141万
 $40,865/呎
-(18年-07月-31日)</t>
+(18年-08月-01日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -26491,7 +26491,7 @@
           <t>D | 379呎 (1房)
 $1293万
 $34,116/呎
-(18年-08月-14日)</t>
+(18年-08月-15日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -26499,7 +26499,7 @@
           <t>E | 369呎 (1房)
 $1250万
 $33,888/呎
-(18年-08月-02日)</t>
+(18年-08月-03日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -26507,7 +26507,7 @@
           <t>F | 286呎 (开放式)
 $1053万
 $36,835/呎
-(20年-12月-13日)</t>
+(20年-12月-14日)</t>
         </is>
       </c>
     </row>
@@ -26522,7 +26522,7 @@
           <t>A | 364呎 (1房)
 $1435万
 $39,418/呎
-(18年-08月-28日)</t>
+(18年-08月-29日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -26530,7 +26530,7 @@
           <t>B | 378呎 (1房)
 $1680万
 $44,433/呎
-(18年-08月-29日)</t>
+(18年-08月-30日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -26538,7 +26538,7 @@
           <t>C | 524呎 (2房)
 $2169万
 $41,392/呎
-(18年-08月-28日)</t>
+(18年-08月-29日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -26546,7 +26546,7 @@
           <t>D | 380呎 (1房)
 $1290万
 $33,939/呎
-(18年-08月-09日)</t>
+(18年-08月-10日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -26554,7 +26554,7 @@
           <t>E | 369呎 (1房)
 $1285万
 $34,819/呎
-(18年-08月-27日)</t>
+(18年-08月-28日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -26562,7 +26562,7 @@
           <t>F | 286呎 (开放式)
 $1051万
 $36,742/呎
-(19年-05月-16日)</t>
+(19年-05月-17日)</t>
         </is>
       </c>
     </row>
@@ -26577,7 +26577,7 @@
           <t>A | 364呎 (1房)
 $1512万
 $41,541/呎
-(18年-07月-30日)</t>
+(18年-07月-31日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -26585,7 +26585,7 @@
           <t>B | 378呎 (1房)
 $1517万
 $40,125/呎
-(18年-07月-30日)</t>
+(18年-07月-31日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -26593,7 +26593,7 @@
           <t>C | 524呎 (2房)
 $2116万
 $40,378/呎
-(18年-08月-05日)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -26601,7 +26601,7 @@
           <t>D | 380呎 (1房)
 $1261万
 $33,191/呎
-(18年-08月-05日)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -26609,7 +26609,7 @@
           <t>E | 369呎 (1房)
 $1220万
 $33,059/呎
-(18年-07月-29日)</t>
+(18年-07月-30日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -26617,7 +26617,7 @@
           <t>F | 286呎 (开放式)
 $1028万
 $35,934/呎
-(18年-08月-02日)</t>
+(18年-08月-03日)</t>
         </is>
       </c>
     </row>
@@ -26632,7 +26632,7 @@
           <t>A | 364呎 (1房)
 $1393万
 $38,261/呎
-(18年-07月-31日)</t>
+(18年-08月-01日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -26640,7 +26640,7 @@
           <t>B | 378呎 (1房)
 $1509万
 $39,926/呎
-(18年-07月-31日)</t>
+(18年-08月-01日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -26648,7 +26648,7 @@
           <t>C | 524呎 (2房)
 $2105万
 $40,175/呎
-(19年-05月-01日)</t>
+(19年-05月-02日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -26656,7 +26656,7 @@
           <t>D | 380呎 (1房)
 $1258万
 $33,110/呎
-(18年-08月-05日)</t>
+(18年-08月-06日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -26664,7 +26664,7 @@
           <t>E | 369呎 (1房)
 $1217万
 $32,975/呎
-(18年-08月-15日)</t>
+(18年-08月-16日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -26672,7 +26672,7 @@
           <t>F | 286呎 (开放式)
 $1025万
 $35,841/呎
-(18年-07月-29日)</t>
+(18年-07月-30日)</t>
         </is>
       </c>
     </row>
@@ -26922,7 +26922,7 @@
           <t>A | 1559呎 (4+房)
 $8141万
 $52,217/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -26930,7 +26930,7 @@
           <t>B | 1446呎 (4+房)
 $6827万
 $47,213/呎
-(25年-06月-15日)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
     </row>
@@ -26976,7 +26976,7 @@
           <t>B | 1446呎 (4+房)
 $6607万
 $45,690/呎
-(25年-08月-03日)</t>
+(25年-08月-04日)</t>
         </is>
       </c>
     </row>
@@ -26991,7 +26991,7 @@
           <t>A | 1559呎 (4+房)
 $8099万
 $51,950/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -26999,7 +26999,7 @@
           <t>B | 1446呎 (4+房)
 $6496万
 $44,926/呎
-(25年-07月-23日)</t>
+(25年-07月-24日)</t>
         </is>
       </c>
     </row>
@@ -27014,7 +27014,7 @@
           <t>A | 1559呎 (4+房)
 $8619万
 $55,284/呎
-(23年-12月-13日)</t>
+(23年-12月-14日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -27022,7 +27022,7 @@
           <t>B | 1446呎 (4+房)
 $6386万
 $44,163/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -27037,7 +27037,7 @@
           <t>A | 1559呎 (4+房)
 $7209万
 $46,241/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -27045,7 +27045,7 @@
           <t>B | 1446呎 (4+房)
 $6279万
 $43,426/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
     </row>
@@ -27060,7 +27060,7 @@
           <t>A | 1559呎 (4+房)
 $7017万
 $45,008/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -27068,7 +27068,7 @@
           <t>B | 1446呎 (4+房)
 $6173万
 $42,690/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
     </row>
@@ -27083,7 +27083,7 @@
           <t>A | 1559呎 (4+房)
 $6825万
 $43,775/呎
-(25年-10月-20日)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -27091,7 +27091,7 @@
           <t>B | 1446呎 (4+房)
 $6072万
 $41,990/呎
-(25年-12月-01日)</t>
+(25年-12月-02日)</t>
         </is>
       </c>
     </row>
@@ -27106,7 +27106,7 @@
           <t>A | 1559呎 (4+房)
 $6632万
 $42,542/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -27129,7 +27129,7 @@
           <t>A | 1559呎 (4+房)
 $6472万
 $41,514/呎
-(25年-08月-07日)</t>
+(25年-08月-08日)</t>
         </is>
       </c>
       <c r="C20" s="24" t="inlineStr">

--- a/files/港岛-北角-海璇.xlsx
+++ b/files/港岛-北角-海璇.xlsx
@@ -14227,7 +14227,7 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>暂停销售</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
@@ -26746,7 +26746,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26761,7 +26761,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -27109,12 +27109,12 @@
 (25年-06月-20日)</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 1488呎 (4+房)
 招标单位
 -
-(在售)</t>
+(暂停销售)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-北角-海璇.xlsx
+++ b/files/港岛-北角-海璇.xlsx
@@ -13405,7 +13405,7 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
@@ -13415,12 +13415,12 @@
       </c>
       <c r="H199" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I199" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J199" s="3" t="inlineStr">
@@ -13430,12 +13430,12 @@
       </c>
       <c r="K199" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L199" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M199" s="3" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="N199" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -14227,38 +14227,30 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H212" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I212" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H212" s="5" t="n">
+        <v>73656000</v>
+      </c>
+      <c r="I212" s="5" t="n">
+        <v>49500</v>
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K212" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L212" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K212" s="5" t="n">
+        <v>73656000</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>49500</v>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
@@ -14267,7 +14259,7 @@
       </c>
       <c r="N212" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26746,7 +26738,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26756,12 +26748,12 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -26940,12 +26932,12 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 1602呎 (4+房)
--
--
-(暂停销售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -27109,12 +27101,12 @@
 (25年-06月-20日)</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 1488呎 (4+房)
-招标单位
--
-(暂停销售)</t>
+$7366万
+$49,500/呎
+(26年-08月-10日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-北角-海璇.xlsx
+++ b/files/港岛-北角-海璇.xlsx
@@ -4191,7 +4191,7 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>2023</v>
+        <v>1973</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
       </c>
       <c r="B6" s="24" t="inlineStr">
         <is>
-          <t>A | 2023呎 (4+房)
+          <t>A | 1973呎 (4+房)
 -
 -
 (待售)</t>

--- a/files/港岛-北角-海璇.xlsx
+++ b/files/港岛-北角-海璇.xlsx
@@ -921,7 +921,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -13335,38 +13335,30 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H198" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I198" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H198" s="5" t="n">
+        <v>83113000</v>
+      </c>
+      <c r="I198" s="5" t="n">
+        <v>55856</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K198" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L198" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K198" s="5" t="n">
+        <v>83113000</v>
+      </c>
+      <c r="L198" s="5" t="n">
+        <v>55856</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
@@ -13375,7 +13367,7 @@
       </c>
       <c r="N198" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -13405,38 +13397,30 @@
       </c>
       <c r="F199" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H199" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I199" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="n">
+        <v>94598000</v>
+      </c>
+      <c r="I199" s="5" t="n">
+        <v>59050</v>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K199" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L199" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K199" s="5" t="n">
+        <v>94598000</v>
+      </c>
+      <c r="L199" s="5" t="n">
+        <v>59050</v>
       </c>
       <c r="M199" s="3" t="inlineStr">
         <is>
@@ -13445,7 +13429,7 @@
       </c>
       <c r="N199" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -13537,7 +13521,7 @@
       </c>
       <c r="F201" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G201" s="3" t="inlineStr">
@@ -13547,12 +13531,12 @@
       </c>
       <c r="H201" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I201" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J201" s="3" t="inlineStr">
@@ -13562,12 +13546,12 @@
       </c>
       <c r="K201" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L201" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M201" s="3" t="inlineStr">
@@ -13577,7 +13561,7 @@
       </c>
       <c r="N201" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -14351,7 +14335,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -14361,12 +14345,12 @@
       </c>
       <c r="H214" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I214" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J214" s="3" t="inlineStr">
@@ -14376,12 +14360,12 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
@@ -14391,7 +14375,7 @@
       </c>
       <c r="N214" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -24363,22 +24347,22 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -24450,12 +24434,12 @@
 (19年-05月-14日)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 1173呎 (3房)
 招标单位
 -
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -26748,7 +26732,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -26758,7 +26742,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -26932,35 +26916,35 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1602呎 (4+房)
+$9460万
+$59,050/呎
+(26年-08月-19日)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1488呎 (4+房)
+$8311万
+$55,856/呎
+(26年-08月-19日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 1602呎 (4+房)
 招标单位
 -
 (在售)</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>B | 1488呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B13" s="24" t="inlineStr">
-        <is>
-          <t>A | 1602呎 (4+房)
--
--
-(待售)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -27124,12 +27108,12 @@
 (25年-08月-08日)</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 1488呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-北角-海璇.xlsx
+++ b/files/港岛-北角-海璇.xlsx
@@ -14207,7 +14207,7 @@
         </is>
       </c>
       <c r="E212" s="4" t="n">
-        <v>1488</v>
+        <v>1446</v>
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
@@ -14216,14 +14216,14 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
         <v>73656000</v>
       </c>
       <c r="I212" s="5" t="n">
-        <v>49500</v>
+        <v>50938</v>
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>73656000</v>
       </c>
       <c r="L212" s="5" t="n">
-        <v>49500</v>
+        <v>50938</v>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
@@ -27087,10 +27087,10 @@
       </c>
       <c r="C19" s="22" t="inlineStr">
         <is>
-          <t>B | 1488呎 (4+房)
+          <t>B | 1446呎 (4+房)
 $7366万
-$49,500/呎
-(26年-08月-10日)</t>
+$50,938/呎
+(26年-08月-25日)</t>
         </is>
       </c>
     </row>
